--- a/Documents/_帶調字符表.xlsx
+++ b/Documents/_帶調字符表.xlsx
@@ -1,21 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\Piau-Im\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B1C431-F3CD-450E-8861-2BBCD5F9406F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A6E52E-965E-4087-A635-65C5E6AF246C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BA5AB4FF-B054-48DC-9DF0-0EECA4A944F2}"/>
+    <workbookView xWindow="-67320" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{BA5AB4FF-B054-48DC-9DF0-0EECA4A944F2}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
-    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
+    <sheet name="韻母標調" sheetId="5" r:id="rId2"/>
+    <sheet name="調符" sheetId="9" r:id="rId3"/>
+    <sheet name="元音標調" sheetId="7" r:id="rId4"/>
+    <sheet name="調號" sheetId="8" r:id="rId5"/>
+    <sheet name="HEX數值" sheetId="4" r:id="rId6"/>
+    <sheet name="DEC數值" sheetId="2" r:id="rId7"/>
+    <sheet name="鼻音韻母" sheetId="3" r:id="rId8"/>
+    <sheet name="字元" sheetId="6" r:id="rId9"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId10"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +47,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -59,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="242">
   <si>
     <t>台羅拼音帶調字符表[1]</t>
   </si>
@@ -682,22 +692,352 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>HEX</t>
+    <t>U+0303</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Mūn cheng-hu í chêng-lō͘, hūn sîn-kong chi hi-bî.​</t>
-  </si>
-  <si>
-    <t>ō͘</t>
+    <t>i</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>a</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>u</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unicode 編碼</t>
+  </si>
+  <si>
+    <t>U+0303</t>
+  </si>
+  <si>
+    <t>ã</t>
+  </si>
+  <si>
+    <t>U+0294</t>
+  </si>
+  <si>
+    <t>aʔ</t>
+  </si>
+  <si>
+    <t>o͘</t>
+  </si>
+  <si>
+    <t>ㄥ</t>
+  </si>
+  <si>
+    <t>ㆭ</t>
+  </si>
+  <si>
+    <t>十進制編碼</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>U+0358</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>拼音字母</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>o</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>組合結果</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ia</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>iau</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>韻母標音</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>簡要格式</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>完整格式</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>əŋ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ə</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ŋ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ŋ̍</t>
+  </si>
+  <si>
+    <t>ŋ̍</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unicode字元</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>註釋</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>台羅調符</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>U+0301</t>
+  </si>
+  <si>
+    <t>U+0300</t>
+  </si>
+  <si>
+    <t>U+0302</t>
+  </si>
+  <si>
+    <t>U+030C</t>
+  </si>
+  <si>
+    <t>U+0304</t>
+  </si>
+  <si>
+    <t>U+030D</t>
+  </si>
+  <si>
+    <t>U+030B</t>
+  </si>
+  <si>
+    <t>二聲（陰上）</t>
+  </si>
+  <si>
+    <t>三聲（陰去）</t>
+  </si>
+  <si>
+    <t>五聲（陽平）</t>
+  </si>
+  <si>
+    <t>六聲（陽上）</t>
+  </si>
+  <si>
+    <t>七聲（陽去）</t>
+  </si>
+  <si>
+    <t>八聲（陽入）</t>
+  </si>
+  <si>
+    <t>九聲</t>
+  </si>
+  <si>
+    <t>字母</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>一聲（陰平）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>四聲（陰入）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>大寫</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>小寫</t>
+    </r>
+  </si>
+  <si>
+    <t>台羅拼音帶調字符表</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>調符 Unicode</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>aɪʔ</t>
+  </si>
+  <si>
+    <t>ʔ</t>
+  </si>
+  <si>
+    <t>ap̚</t>
+  </si>
+  <si>
+    <t>附註</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>入聲韻尾 h</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>aʊ</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>aɪ</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ʊ</t>
+  </si>
+  <si>
+    <t>ɪ</t>
+  </si>
+  <si>
+    <t>ɛ</t>
+  </si>
+  <si>
+    <t>ɔ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>m̩</t>
+  </si>
+  <si>
+    <t>閩拼調符</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>三聲（陰上）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>二聲（陽平）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>七聲（陰入）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>八聲（陽入）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>五聲（陰去）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>六聲（陽去）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>̚</t>
+  </si>
+  <si>
+    <t>̃</t>
+  </si>
+  <si>
+    <t>ⁿ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>a</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>i</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>u</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>e</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>o</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>m</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>n</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>調號</t>
+  </si>
+  <si>
+    <t>上標值</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>¹</t>
+  </si>
+  <si>
+    <t>²</t>
+  </si>
+  <si>
+    <t>³</t>
+  </si>
+  <si>
+    <t>⁴</t>
+  </si>
+  <si>
+    <t>⁵</t>
+  </si>
+  <si>
+    <t>⁶</t>
+  </si>
+  <si>
+    <t>⁷</t>
+  </si>
+  <si>
+    <t>⁸</t>
+  </si>
+  <si>
+    <t>⁹</t>
+  </si>
+  <si>
+    <t>⁰</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -746,8 +1086,126 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Noto Sans TC Medium"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="Noto Sans TC"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei UI"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color rgb="FFFF0000"/>
+      <name val="Noto Sans TC"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Charis SIL"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Noto Sans HK"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFC00000"/>
+      <name val="Noto Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Charis Medium"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Charis Medium"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Charis Medium"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="Noto Sans TC Medium"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -766,8 +1224,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -775,13 +1251,116 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE2E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE2E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDEE2E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDEE2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -812,11 +1391,225 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="一般 4" xfId="1" xr:uid="{D629CA5E-3DFD-4E1C-9105-69B043227C53}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -832,6 +1625,184 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="聲表"/>
+      <sheetName val="韻表"/>
+      <sheetName val="調表"/>
+      <sheetName val="台羅國際音標對照表"/>
+      <sheetName val="台羅韻母列表"/>
+      <sheetName val="台羅韻母清單"/>
+      <sheetName val="【十五音】韻母對照表"/>
+      <sheetName val="IPA音節表"/>
+      <sheetName val="對照表【工作稿】 "/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="3">
+          <cell r="M3" t="str">
+            <v>台羅調符編碼</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="O4" t="str">
+            <v>U+0304</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="E5" t="str">
+            <v>U+0301</v>
+          </cell>
+          <cell r="M5" t="str">
+            <v>U+0304</v>
+          </cell>
+          <cell r="O5" t="str">
+            <v>U+0302</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="E6" t="str">
+            <v>U+0300</v>
+          </cell>
+          <cell r="M6" t="str">
+            <v>U+0301</v>
+          </cell>
+          <cell r="O6" t="str">
+            <v>U+0300</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="M7" t="str">
+            <v>U+0300</v>
+          </cell>
+          <cell r="O7" t="str">
+            <v>U+030C</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="E8" t="str">
+            <v>U+030C</v>
+          </cell>
+          <cell r="M8" t="str">
+            <v>U+0301</v>
+          </cell>
+          <cell r="O8" t="str">
+            <v>U+0301</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="E9" t="str">
+            <v>U+0301</v>
+          </cell>
+          <cell r="M9" t="str">
+            <v>U+030C</v>
+          </cell>
+          <cell r="O9" t="str">
+            <v>U+0304</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="E10" t="str">
+            <v>U+0304</v>
+          </cell>
+          <cell r="M10" t="str">
+            <v>U+030D</v>
+          </cell>
+          <cell r="O10" t="str">
+            <v>U+0301</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="E11" t="str">
+            <v>U+030D</v>
+          </cell>
+          <cell r="M11" t="str">
+            <v>U+0301</v>
+          </cell>
+          <cell r="O11" t="str">
+            <v>U+030C</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="E12" t="str">
+            <v>U+030B</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="E13" t="str">
+            <v>U+030A</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="E17" t="str">
+            <v>U+0304</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="E18" t="str">
+            <v>U+0301</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v>U+030C</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="E20" t="str">
+            <v>U+030C</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21" t="str">
+            <v>U+0300</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="E22" t="str">
+            <v>U+0302</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="E23" t="str">
+            <v>U+0304</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="E24" t="str">
+            <v>U+0301</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D43B5A57-642A-43D6-A2A7-B725D195B9D5}" name="上標對照表" displayName="上標對照表" ref="B2:C12" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="5" tableBorderDxfId="6" totalsRowBorderDxfId="4">
+  <autoFilter ref="B2:C12" xr:uid="{D43B5A57-642A-43D6-A2A7-B725D195B9D5}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{5A84100E-17CD-4672-9892-D5E8F7F7C8B3}" name="調號" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{70FBA500-FBAD-4731-9062-C41EA2692621}" name="上標值" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1154,7 +2125,8 @@
   <dimension ref="A2:K146"/>
   <sheetFormatPr defaultRowHeight="25.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="9" style="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="23.125" style="1" customWidth="1"/>
     <col min="4" max="7" width="26.875" style="1" customWidth="1"/>
     <col min="8" max="8" width="40.25" style="1" customWidth="1"/>
     <col min="9" max="11" width="26.875" style="1" customWidth="1"/>
@@ -1649,7 +2621,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="4" t="str">
-        <f t="shared" ref="D21:D29" ca="1" si="0" xml:space="preserve"> LEFT(H21)</f>
+        <f t="shared" ref="D21:D27" ca="1" si="0" xml:space="preserve"> LEFT(H21)</f>
         <v>A</v>
       </c>
       <c r="E21" s="6" t="str">
@@ -3494,7 +4466,7 @@
         <v>1</v>
       </c>
       <c r="D66" s="5" t="str">
-        <f t="shared" ref="D66:D72" ca="1" si="17" xml:space="preserve"> LEFT(H66)</f>
+        <f t="shared" ref="D66:D69" ca="1" si="17" xml:space="preserve"> LEFT(H66)</f>
         <v>M</v>
       </c>
       <c r="E66" s="6" t="str">
@@ -3863,7 +4835,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="4" t="str">
-        <f t="shared" ref="D75:D81" ca="1" si="20" xml:space="preserve"> LEFT(H75)</f>
+        <f t="shared" ref="D75:D80" ca="1" si="20" xml:space="preserve"> LEFT(H75)</f>
         <v>N</v>
       </c>
       <c r="E75" s="6" t="str">
@@ -6077,7 +7049,7 @@
         <v>1</v>
       </c>
       <c r="D129" s="5" t="str">
-        <f t="shared" ref="D129:D135" ca="1" si="41" xml:space="preserve"> LEFT(H129)</f>
+        <f t="shared" ref="D129:D132" ca="1" si="41" xml:space="preserve"> LEFT(H129)</f>
         <v>m</v>
       </c>
       <c r="E129" s="6" t="str">
@@ -6446,7 +7418,7 @@
         <v>1</v>
       </c>
       <c r="D138" s="4" t="str">
-        <f t="shared" ref="D138:D144" ca="1" si="44" xml:space="preserve"> LEFT(H138)</f>
+        <f t="shared" ref="D138:D143" ca="1" si="44" xml:space="preserve"> LEFT(H138)</f>
         <v>n</v>
       </c>
       <c r="E138" s="6" t="str">
@@ -6810,67 +7782,3245 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDE21D6C-42DF-494D-A346-039E570FFD2A}">
-  <dimension ref="B1:D9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5633B8F5-09C6-400C-9F20-55BDD652E581}">
+  <dimension ref="B2:R18"/>
+  <sheetFormatPr defaultRowHeight="25.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5" style="1" customWidth="1"/>
+    <col min="3" max="12" width="18.125" style="23" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="I3" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="J3" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="K3" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="L3" s="24" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="G4" s="21"/>
+      <c r="H4" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="I4" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C5, _xlfn.UNICHAR(HEX2DEC(RIGHT(E$4,4))))</f>
+        <v>á</v>
+      </c>
+      <c r="F5" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C5, _xlfn.UNICHAR(HEX2DEC(RIGHT(F$4,4))))</f>
+        <v>à</v>
+      </c>
+      <c r="G5" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C5, "h")</f>
+        <v>ah</v>
+      </c>
+      <c r="H5" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C5, _xlfn.UNICHAR(HEX2DEC(RIGHT(H$4,4))))</f>
+        <v>â</v>
+      </c>
+      <c r="I5" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C5, _xlfn.UNICHAR(HEX2DEC(RIGHT(I$4,4))))</f>
+        <v>ǎ</v>
+      </c>
+      <c r="J5" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C5, _xlfn.UNICHAR(HEX2DEC(RIGHT(J$4,4))))</f>
+        <v>ā</v>
+      </c>
+      <c r="K5" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C5, _xlfn.UNICHAR(HEX2DEC(RIGHT(K$4,4))), "h")</f>
+        <v>a̍h</v>
+      </c>
+      <c r="L5" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C5, _xlfn.UNICHAR(HEX2DEC(RIGHT(L$4,4))))</f>
+        <v>a̋</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="20"/>
+      <c r="C6" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C6, _xlfn.UNICHAR(HEX2DEC(RIGHT(E$4,4))))</f>
+        <v>é</v>
+      </c>
+      <c r="F6" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C6, _xlfn.UNICHAR(HEX2DEC(RIGHT(F$4,4))))</f>
+        <v>è</v>
+      </c>
+      <c r="G6" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C6, "h")</f>
+        <v>eh</v>
+      </c>
+      <c r="H6" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C6, _xlfn.UNICHAR(HEX2DEC(RIGHT(H$4,4))))</f>
+        <v>ê</v>
+      </c>
+      <c r="I6" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C6, _xlfn.UNICHAR(HEX2DEC(RIGHT(I$4,4))))</f>
+        <v>ě</v>
+      </c>
+      <c r="J6" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C6, _xlfn.UNICHAR(HEX2DEC(RIGHT(J$4,4))))</f>
+        <v>ē</v>
+      </c>
+      <c r="K6" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C6, _xlfn.UNICHAR(HEX2DEC(RIGHT(K$4,4))), "h")</f>
+        <v>e̍h</v>
+      </c>
+      <c r="L6" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C6, _xlfn.UNICHAR(HEX2DEC(RIGHT(L$4,4))))</f>
+        <v>e̋</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="20"/>
+      <c r="C7" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C7, _xlfn.UNICHAR(HEX2DEC(RIGHT(E$4,4))))</f>
+        <v>í</v>
+      </c>
+      <c r="F7" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C7, _xlfn.UNICHAR(HEX2DEC(RIGHT(F$4,4))))</f>
+        <v>ì</v>
+      </c>
+      <c r="G7" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C7, "h")</f>
+        <v>ih</v>
+      </c>
+      <c r="H7" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C7, _xlfn.UNICHAR(HEX2DEC(RIGHT(H$4,4))))</f>
+        <v>î</v>
+      </c>
+      <c r="I7" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C7, _xlfn.UNICHAR(HEX2DEC(RIGHT(I$4,4))))</f>
+        <v>ǐ</v>
+      </c>
+      <c r="J7" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C7, _xlfn.UNICHAR(HEX2DEC(RIGHT(J$4,4))))</f>
+        <v>ī</v>
+      </c>
+      <c r="K7" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C7, _xlfn.UNICHAR(HEX2DEC(RIGHT(K$4,4))), "h")</f>
+        <v>i̍h</v>
+      </c>
+      <c r="L7" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C7, _xlfn.UNICHAR(HEX2DEC(RIGHT(L$4,4))))</f>
+        <v>i̋</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="20"/>
+      <c r="C8" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C8, _xlfn.UNICHAR(HEX2DEC(RIGHT(E$4,4))))</f>
+        <v>ó</v>
+      </c>
+      <c r="F8" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C8, _xlfn.UNICHAR(HEX2DEC(RIGHT(F$4,4))))</f>
+        <v>ò</v>
+      </c>
+      <c r="G8" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C8, "h")</f>
+        <v>oh</v>
+      </c>
+      <c r="H8" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C8, _xlfn.UNICHAR(HEX2DEC(RIGHT(H$4,4))))</f>
+        <v>ô</v>
+      </c>
+      <c r="I8" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C8, _xlfn.UNICHAR(HEX2DEC(RIGHT(I$4,4))))</f>
+        <v>ǒ</v>
+      </c>
+      <c r="J8" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C8, _xlfn.UNICHAR(HEX2DEC(RIGHT(J$4,4))))</f>
+        <v>ō</v>
+      </c>
+      <c r="K8" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C8, _xlfn.UNICHAR(HEX2DEC(RIGHT(K$4,4))), "h")</f>
+        <v>o̍h</v>
+      </c>
+      <c r="L8" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C8, _xlfn.UNICHAR(HEX2DEC(RIGHT(L$4,4))))</f>
+        <v>ő</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="20"/>
+      <c r="C9" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="E9" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C9, _xlfn.UNICHAR(HEX2DEC(RIGHT(E$4,4))))</f>
+        <v>ú</v>
+      </c>
+      <c r="F9" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C9, _xlfn.UNICHAR(HEX2DEC(RIGHT(F$4,4))))</f>
+        <v>ù</v>
+      </c>
+      <c r="G9" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C9, "h")</f>
+        <v>uh</v>
+      </c>
+      <c r="H9" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C9, _xlfn.UNICHAR(HEX2DEC(RIGHT(H$4,4))))</f>
+        <v>û</v>
+      </c>
+      <c r="I9" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C9, _xlfn.UNICHAR(HEX2DEC(RIGHT(I$4,4))))</f>
+        <v>ǔ</v>
+      </c>
+      <c r="J9" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C9, _xlfn.UNICHAR(HEX2DEC(RIGHT(J$4,4))))</f>
+        <v>ū</v>
+      </c>
+      <c r="K9" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C9, _xlfn.UNICHAR(HEX2DEC(RIGHT(K$4,4))), "h")</f>
+        <v>u̍h</v>
+      </c>
+      <c r="L9" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C9, _xlfn.UNICHAR(HEX2DEC(RIGHT(L$4,4))))</f>
+        <v>ű</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="20"/>
+      <c r="C10" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="E10" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C10, _xlfn.UNICHAR(HEX2DEC(RIGHT(E$4,4))))</f>
+        <v>ḿ</v>
+      </c>
+      <c r="F10" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C10, _xlfn.UNICHAR(HEX2DEC(RIGHT(F$4,4))))</f>
+        <v>m̀</v>
+      </c>
+      <c r="G10" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C10, "h")</f>
+        <v>mh</v>
+      </c>
+      <c r="H10" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C10, _xlfn.UNICHAR(HEX2DEC(RIGHT(H$4,4))))</f>
+        <v>m̂</v>
+      </c>
+      <c r="I10" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C10, _xlfn.UNICHAR(HEX2DEC(RIGHT(I$4,4))))</f>
+        <v>m̌</v>
+      </c>
+      <c r="J10" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C10, _xlfn.UNICHAR(HEX2DEC(RIGHT(J$4,4))))</f>
+        <v>m̄</v>
+      </c>
+      <c r="K10" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C10, _xlfn.UNICHAR(HEX2DEC(RIGHT(K$4,4))), "h")</f>
+        <v>m̍h</v>
+      </c>
+      <c r="L10" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C10, _xlfn.UNICHAR(HEX2DEC(RIGHT(L$4,4))))</f>
+        <v>m̋</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="20"/>
+      <c r="C11" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C11, _xlfn.UNICHAR(HEX2DEC(RIGHT(E$4,4))))</f>
+        <v>ń</v>
+      </c>
+      <c r="F11" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C11, _xlfn.UNICHAR(HEX2DEC(RIGHT(F$4,4))))</f>
+        <v>ǹ</v>
+      </c>
+      <c r="G11" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C11, "h")</f>
+        <v>nh</v>
+      </c>
+      <c r="H11" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C11, _xlfn.UNICHAR(HEX2DEC(RIGHT(H$4,4))))</f>
+        <v>n̂</v>
+      </c>
+      <c r="I11" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C11, _xlfn.UNICHAR(HEX2DEC(RIGHT(I$4,4))))</f>
+        <v>ň</v>
+      </c>
+      <c r="J11" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C11, _xlfn.UNICHAR(HEX2DEC(RIGHT(J$4,4))))</f>
+        <v>n̄</v>
+      </c>
+      <c r="K11" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C11, _xlfn.UNICHAR(HEX2DEC(RIGHT(K$4,4))), "h")</f>
+        <v>n̍h</v>
+      </c>
+      <c r="L11" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C11, _xlfn.UNICHAR(HEX2DEC(RIGHT(L$4,4))))</f>
+        <v>n̋</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C12, _xlfn.UNICHAR(HEX2DEC(RIGHT(E$4,4))))</f>
+        <v>Á</v>
+      </c>
+      <c r="F12" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C12, _xlfn.UNICHAR(HEX2DEC(RIGHT(F$4,4))))</f>
+        <v>À</v>
+      </c>
+      <c r="G12" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C12, "h")</f>
+        <v>Ah</v>
+      </c>
+      <c r="H12" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C12, _xlfn.UNICHAR(HEX2DEC(RIGHT(H$4,4))))</f>
+        <v>Â</v>
+      </c>
+      <c r="I12" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C12, _xlfn.UNICHAR(HEX2DEC(RIGHT(I$4,4))))</f>
+        <v>Ǎ</v>
+      </c>
+      <c r="J12" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C12, _xlfn.UNICHAR(HEX2DEC(RIGHT(J$4,4))))</f>
+        <v>Ā</v>
+      </c>
+      <c r="K12" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C12, _xlfn.UNICHAR(HEX2DEC(RIGHT(K$4,4))), "h")</f>
+        <v>A̍h</v>
+      </c>
+      <c r="L12" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C12, _xlfn.UNICHAR(HEX2DEC(RIGHT(L$4,4))))</f>
+        <v>A̋</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="20"/>
+      <c r="C13" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C13, _xlfn.UNICHAR(HEX2DEC(RIGHT(E$4,4))))</f>
+        <v>É</v>
+      </c>
+      <c r="F13" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C13, _xlfn.UNICHAR(HEX2DEC(RIGHT(F$4,4))))</f>
+        <v>È</v>
+      </c>
+      <c r="G13" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C13, "h")</f>
+        <v>Eh</v>
+      </c>
+      <c r="H13" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C13, _xlfn.UNICHAR(HEX2DEC(RIGHT(H$4,4))))</f>
+        <v>Ê</v>
+      </c>
+      <c r="I13" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C13, _xlfn.UNICHAR(HEX2DEC(RIGHT(I$4,4))))</f>
+        <v>Ě</v>
+      </c>
+      <c r="J13" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C13, _xlfn.UNICHAR(HEX2DEC(RIGHT(J$4,4))))</f>
+        <v>Ē</v>
+      </c>
+      <c r="K13" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C13, _xlfn.UNICHAR(HEX2DEC(RIGHT(K$4,4))), "h")</f>
+        <v>E̍h</v>
+      </c>
+      <c r="L13" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C13, _xlfn.UNICHAR(HEX2DEC(RIGHT(L$4,4))))</f>
+        <v>E̋</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="20"/>
+      <c r="C14" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C14, _xlfn.UNICHAR(HEX2DEC(RIGHT(E$4,4))))</f>
+        <v>Í</v>
+      </c>
+      <c r="F14" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C14, _xlfn.UNICHAR(HEX2DEC(RIGHT(F$4,4))))</f>
+        <v>Ì</v>
+      </c>
+      <c r="G14" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C14, "h")</f>
+        <v>Ih</v>
+      </c>
+      <c r="H14" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C14, _xlfn.UNICHAR(HEX2DEC(RIGHT(H$4,4))))</f>
+        <v>Î</v>
+      </c>
+      <c r="I14" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C14, _xlfn.UNICHAR(HEX2DEC(RIGHT(I$4,4))))</f>
+        <v>Ǐ</v>
+      </c>
+      <c r="J14" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C14, _xlfn.UNICHAR(HEX2DEC(RIGHT(J$4,4))))</f>
+        <v>Ī</v>
+      </c>
+      <c r="K14" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C14, _xlfn.UNICHAR(HEX2DEC(RIGHT(K$4,4))), "h")</f>
+        <v>I̍h</v>
+      </c>
+      <c r="L14" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C14, _xlfn.UNICHAR(HEX2DEC(RIGHT(L$4,4))))</f>
+        <v>I̋</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="20"/>
+      <c r="C15" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C15, _xlfn.UNICHAR(HEX2DEC(RIGHT(E$4,4))))</f>
+        <v>Ó</v>
+      </c>
+      <c r="F15" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C15, _xlfn.UNICHAR(HEX2DEC(RIGHT(F$4,4))))</f>
+        <v>Ò</v>
+      </c>
+      <c r="G15" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C15, "h")</f>
+        <v>Oh</v>
+      </c>
+      <c r="H15" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C15, _xlfn.UNICHAR(HEX2DEC(RIGHT(H$4,4))))</f>
+        <v>Ô</v>
+      </c>
+      <c r="I15" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C15, _xlfn.UNICHAR(HEX2DEC(RIGHT(I$4,4))))</f>
+        <v>Ǒ</v>
+      </c>
+      <c r="J15" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C15, _xlfn.UNICHAR(HEX2DEC(RIGHT(J$4,4))))</f>
+        <v>Ō</v>
+      </c>
+      <c r="K15" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C15, _xlfn.UNICHAR(HEX2DEC(RIGHT(K$4,4))), "h")</f>
+        <v>O̍h</v>
+      </c>
+      <c r="L15" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C15, _xlfn.UNICHAR(HEX2DEC(RIGHT(L$4,4))))</f>
+        <v>Ő</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="20"/>
+      <c r="C16" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C16, _xlfn.UNICHAR(HEX2DEC(RIGHT(E$4,4))))</f>
+        <v>Ú</v>
+      </c>
+      <c r="F16" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C16, _xlfn.UNICHAR(HEX2DEC(RIGHT(F$4,4))))</f>
+        <v>Ù</v>
+      </c>
+      <c r="G16" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C16, "h")</f>
+        <v>Uh</v>
+      </c>
+      <c r="H16" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C16, _xlfn.UNICHAR(HEX2DEC(RIGHT(H$4,4))))</f>
+        <v>Û</v>
+      </c>
+      <c r="I16" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C16, _xlfn.UNICHAR(HEX2DEC(RIGHT(I$4,4))))</f>
+        <v>Ǔ</v>
+      </c>
+      <c r="J16" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C16, _xlfn.UNICHAR(HEX2DEC(RIGHT(J$4,4))))</f>
+        <v>Ū</v>
+      </c>
+      <c r="K16" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C16, _xlfn.UNICHAR(HEX2DEC(RIGHT(K$4,4))), "h")</f>
+        <v>U̍h</v>
+      </c>
+      <c r="L16" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C16, _xlfn.UNICHAR(HEX2DEC(RIGHT(L$4,4))))</f>
+        <v>Ű</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="20"/>
+      <c r="C17" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C17, _xlfn.UNICHAR(HEX2DEC(RIGHT(E$4,4))))</f>
+        <v>Ḿ</v>
+      </c>
+      <c r="F17" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C17, _xlfn.UNICHAR(HEX2DEC(RIGHT(F$4,4))))</f>
+        <v>M̀</v>
+      </c>
+      <c r="G17" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C17, "h")</f>
+        <v>Mh</v>
+      </c>
+      <c r="H17" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C17, _xlfn.UNICHAR(HEX2DEC(RIGHT(H$4,4))))</f>
+        <v>M̂</v>
+      </c>
+      <c r="I17" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C17, _xlfn.UNICHAR(HEX2DEC(RIGHT(I$4,4))))</f>
+        <v>M̌</v>
+      </c>
+      <c r="J17" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C17, _xlfn.UNICHAR(HEX2DEC(RIGHT(J$4,4))))</f>
+        <v>M̄</v>
+      </c>
+      <c r="K17" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C17, _xlfn.UNICHAR(HEX2DEC(RIGHT(K$4,4))), "h")</f>
+        <v>M̍h</v>
+      </c>
+      <c r="L17" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C17, _xlfn.UNICHAR(HEX2DEC(RIGHT(L$4,4))))</f>
+        <v>M̋</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="20"/>
+      <c r="C18" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C18, _xlfn.UNICHAR(HEX2DEC(RIGHT(E$4,4))))</f>
+        <v>Ń</v>
+      </c>
+      <c r="F18" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C18, _xlfn.UNICHAR(HEX2DEC(RIGHT(F$4,4))))</f>
+        <v>Ǹ</v>
+      </c>
+      <c r="G18" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C18, "h")</f>
+        <v>Nh</v>
+      </c>
+      <c r="H18" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C18, _xlfn.UNICHAR(HEX2DEC(RIGHT(H$4,4))))</f>
+        <v>N̂</v>
+      </c>
+      <c r="I18" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C18, _xlfn.UNICHAR(HEX2DEC(RIGHT(I$4,4))))</f>
+        <v>Ň</v>
+      </c>
+      <c r="J18" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C18, _xlfn.UNICHAR(HEX2DEC(RIGHT(J$4,4))))</f>
+        <v>N̄</v>
+      </c>
+      <c r="K18" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C18, _xlfn.UNICHAR(HEX2DEC(RIGHT(K$4,4))), "h")</f>
+        <v>N̍h</v>
+      </c>
+      <c r="L18" s="25" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($C18, _xlfn.UNICHAR(HEX2DEC(RIGHT(L$4,4))))</f>
+        <v>N̋</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="G5" formula="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69E21FE1-8FBB-45A1-8B7F-E62039CF8C70}">
+  <dimension ref="A2:F22"/>
+  <sheetFormatPr defaultRowHeight="25.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="32.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="22.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="45.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" spans="2:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="2:5" ht="45.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" s="16" t="str">
+        <f>_xlfn.CONCAT(C5,_xlfn.UNICHAR(HEX2DEC(RIGHT(B5,4))))</f>
+        <v>á</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" s="16" t="str">
+        <f>_xlfn.CONCAT(C6,_xlfn.UNICHAR(HEX2DEC(RIGHT(B6,4))))</f>
+        <v>à</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="16" t="str">
+        <f>_xlfn.CONCAT(C7,_xlfn.UNICHAR(HEX2DEC(RIGHT(B7,4))))</f>
+        <v>â</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="16" t="str">
+        <f>_xlfn.CONCAT(C8,_xlfn.UNICHAR(HEX2DEC(RIGHT(B8,4))))</f>
+        <v>ǎ</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D9" s="16" t="str">
+        <f>_xlfn.CONCAT(C9,_xlfn.UNICHAR(HEX2DEC(RIGHT(B9,4))))</f>
+        <v>ā</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" s="16" t="str">
+        <f>_xlfn.CONCAT(C10,_xlfn.UNICHAR(HEX2DEC(RIGHT(B10,4))))</f>
+        <v>a̍</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="16" t="str">
+        <f>_xlfn.CONCAT(C11,_xlfn.UNICHAR(HEX2DEC(RIGHT(B11,4))))</f>
+        <v>a̋</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="2:5" ht="45.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="2:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="2:5" ht="45.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D16" s="16" t="str">
+        <f>_xlfn.CONCAT(C16,_xlfn.UNICHAR(HEX2DEC(RIGHT(B16,4))))</f>
+        <v>ā</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" s="16" t="str">
+        <f>_xlfn.CONCAT(C17,_xlfn.UNICHAR(HEX2DEC(RIGHT(B17,4))))</f>
+        <v>á</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" s="16" t="str">
+        <f>_xlfn.CONCAT(C18,_xlfn.UNICHAR(HEX2DEC(RIGHT(B18,4))))</f>
+        <v>ǎ</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="16" t="str">
+        <f>_xlfn.CONCAT(C19,_xlfn.UNICHAR(HEX2DEC(RIGHT(B19,4))))</f>
+        <v>à</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D20" s="16" t="str">
+        <f>_xlfn.CONCAT(C20,_xlfn.UNICHAR(HEX2DEC(RIGHT(B20,4))))</f>
+        <v>â</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D21" s="16" t="str">
+        <f>_xlfn.CONCAT(C21,_xlfn.UNICHAR(HEX2DEC(RIGHT(B21,4))),"h")</f>
+        <v>āh</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" s="16" t="str">
+        <f>_xlfn.CONCAT(C22,_xlfn.UNICHAR(HEX2DEC(RIGHT(B22,4))),"h")</f>
+        <v>áh</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6541E4-ECDA-4432-B6E5-AF77031DB825}">
+  <dimension ref="A2:M36"/>
+  <sheetFormatPr defaultRowHeight="36.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.25" style="32" customWidth="1"/>
+    <col min="2" max="2" width="3.25" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="11" width="10.625" style="29" customWidth="1"/>
+    <col min="12" max="13" width="9" style="30"/>
+    <col min="14" max="16384" width="9" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="C2" s="33" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))))</f>
+        <v>o͘</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="F2" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="J2" s="34" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B3" s="29">
+        <v>1</v>
+      </c>
+      <c r="C3" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!E4,4)))), $C$2)</f>
+        <v>o͘</v>
+      </c>
+      <c r="D3" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E4,4))))), "")</f>
+        <v>a</v>
+      </c>
+      <c r="E3" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E4,4))))), "")</f>
+        <v>i</v>
+      </c>
+      <c r="F3" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E4,4))))), "")</f>
+        <v>u</v>
+      </c>
+      <c r="G3" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E4,4))))), "")</f>
+        <v>e</v>
+      </c>
+      <c r="H3" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E4,4))))), "")</f>
+        <v>o</v>
+      </c>
+      <c r="I3" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E4,4))))), "")</f>
+        <v>m</v>
+      </c>
+      <c r="J3" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E4,4))))), "")</f>
+        <v>n</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B4" s="29">
+        <v>2</v>
+      </c>
+      <c r="C4" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!E5,4)))), $C$2)</f>
+        <v>ó͘</v>
+      </c>
+      <c r="D4" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E5,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="E4" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E5,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="F4" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E5,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="G4" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E5,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="H4" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E5,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="I4" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E5,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="J4" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E5,4))))), "")</f>
+        <v>ń</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="29">
+        <v>3</v>
+      </c>
+      <c r="C5" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!E6,4)))), $C$2)</f>
+        <v>ò͘</v>
+      </c>
+      <c r="D5" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E6,4))))), "")</f>
+        <v>à</v>
+      </c>
+      <c r="E5" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E6,4))))), "")</f>
+        <v>ì</v>
+      </c>
+      <c r="F5" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E6,4))))), "")</f>
+        <v>ù</v>
+      </c>
+      <c r="G5" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E6,4))))), "")</f>
+        <v>è</v>
+      </c>
+      <c r="H5" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E6,4))))), "")</f>
+        <v>ò</v>
+      </c>
+      <c r="I5" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E6,4))))), "")</f>
+        <v>m̀</v>
+      </c>
+      <c r="J5" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E6,4))))), "")</f>
+        <v>ǹ</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="29">
+        <v>4</v>
+      </c>
+      <c r="C6" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!E7,4)))), $C$2)</f>
+        <v>o͘</v>
+      </c>
+      <c r="D6" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E7,4))))), "")</f>
+        <v>a</v>
+      </c>
+      <c r="E6" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E7,4))))), "")</f>
+        <v>i</v>
+      </c>
+      <c r="F6" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E7,4))))), "")</f>
+        <v>u</v>
+      </c>
+      <c r="G6" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E7,4))))), "")</f>
+        <v>e</v>
+      </c>
+      <c r="H6" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E7,4))))), "")</f>
+        <v>o</v>
+      </c>
+      <c r="I6" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E7,4))))), "")</f>
+        <v>m</v>
+      </c>
+      <c r="J6" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E7,4))))), "")</f>
+        <v>n</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="29">
+        <v>5</v>
+      </c>
+      <c r="C7" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!E8,4)))), "")</f>
+        <v>ǒ͘</v>
+      </c>
+      <c r="D7" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E8,4))))), "")</f>
+        <v>ǎ</v>
+      </c>
+      <c r="E7" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E8,4))))), "")</f>
+        <v>ǐ</v>
+      </c>
+      <c r="F7" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E8,4))))), "")</f>
+        <v>ǔ</v>
+      </c>
+      <c r="G7" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E8,4))))), "")</f>
+        <v>ě</v>
+      </c>
+      <c r="H7" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E8,4))))), "")</f>
+        <v>ǒ</v>
+      </c>
+      <c r="I7" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E8,4))))), "")</f>
+        <v>m̌</v>
+      </c>
+      <c r="J7" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E8,4))))), "")</f>
+        <v>ň</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="29">
+        <v>6</v>
+      </c>
+      <c r="C8" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!E9,4)))), "")</f>
+        <v>ó͘</v>
+      </c>
+      <c r="D8" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E9,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="E8" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E9,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="F8" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E9,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="G8" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E9,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="H8" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E9,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="I8" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E9,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="J8" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E9,4))))), "")</f>
+        <v>ń</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="29">
+        <v>7</v>
+      </c>
+      <c r="C9" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!E10,4)))), "")</f>
+        <v>ō͘</v>
+      </c>
+      <c r="D9" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E10,4))))), "")</f>
+        <v>ā</v>
+      </c>
+      <c r="E9" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E10,4))))), "")</f>
+        <v>ī</v>
+      </c>
+      <c r="F9" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E10,4))))), "")</f>
+        <v>ū</v>
+      </c>
+      <c r="G9" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E10,4))))), "")</f>
+        <v>ē</v>
+      </c>
+      <c r="H9" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E10,4))))), "")</f>
+        <v>ō</v>
+      </c>
+      <c r="I9" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E10,4))))), "")</f>
+        <v>m̄</v>
+      </c>
+      <c r="J9" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E10,4))))), "")</f>
+        <v>n̄</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="29">
+        <v>8</v>
+      </c>
+      <c r="C10" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!E11,4)))), "")</f>
+        <v>o̍͘</v>
+      </c>
+      <c r="D10" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E11,4))))), "")</f>
+        <v>a̍</v>
+      </c>
+      <c r="E10" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E11,4))))), "")</f>
+        <v>i̍</v>
+      </c>
+      <c r="F10" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E11,4))))), "")</f>
+        <v>u̍</v>
+      </c>
+      <c r="G10" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E11,4))))), "")</f>
+        <v>e̍</v>
+      </c>
+      <c r="H10" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E11,4))))), "")</f>
+        <v>o̍</v>
+      </c>
+      <c r="I10" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E11,4))))), "")</f>
+        <v>m̍</v>
+      </c>
+      <c r="J10" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E11,4))))), "")</f>
+        <v>n̍</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="29">
+        <v>9</v>
+      </c>
+      <c r="C11" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!E12,4)))), "")</f>
+        <v>ő͘</v>
+      </c>
+      <c r="D11" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E12,4))))), "")</f>
+        <v>a̋</v>
+      </c>
+      <c r="E11" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E12,4))))), "")</f>
+        <v>i̋</v>
+      </c>
+      <c r="F11" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E12,4))))), "")</f>
+        <v>ű</v>
+      </c>
+      <c r="G11" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E12,4))))), "")</f>
+        <v>e̋</v>
+      </c>
+      <c r="H11" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E12,4))))), "")</f>
+        <v>ő</v>
+      </c>
+      <c r="I11" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E12,4))))), "")</f>
+        <v>m̋</v>
+      </c>
+      <c r="J11" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E12,4))))), "")</f>
+        <v>n̋</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="29">
+        <v>0</v>
+      </c>
+      <c r="C12" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!E13,4)))), "")</f>
+        <v>o̊͘</v>
+      </c>
+      <c r="D12" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E13,4))))), "")</f>
+        <v>å</v>
+      </c>
+      <c r="E12" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E13,4))))), "")</f>
+        <v>i̊</v>
+      </c>
+      <c r="F12" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E13,4))))), "")</f>
+        <v>ů</v>
+      </c>
+      <c r="G12" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E13,4))))), "")</f>
+        <v>e̊</v>
+      </c>
+      <c r="H12" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E13,4))))), "")</f>
+        <v>o̊</v>
+      </c>
+      <c r="I12" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E13,4))))), "")</f>
+        <v>m̊</v>
+      </c>
+      <c r="J12" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E13,4))))), "")</f>
+        <v>n̊</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="29"/>
+      <c r="C15" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="G15" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="H15" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="L15" s="30" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$O4,4))), "n"), "")</f>
+        <v>lūn</v>
+      </c>
+      <c r="M15" s="30" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$O4,4))), "o"), "")</f>
+        <v>ngōo</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="29">
+        <v>1</v>
+      </c>
+      <c r="C16" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E17,4))))), "")</f>
+        <v>ā</v>
+      </c>
+      <c r="D16" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E17,4))))), "")</f>
+        <v>ī</v>
+      </c>
+      <c r="E16" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E17,4))))), "")</f>
+        <v>ū</v>
+      </c>
+      <c r="F16" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E17,4))))), "")</f>
+        <v>ē</v>
+      </c>
+      <c r="G16" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E17,4))))), "")</f>
+        <v>ō</v>
+      </c>
+      <c r="H16" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E17,4))))), "")</f>
+        <v>m̄</v>
+      </c>
+      <c r="I16" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E17,4))))), "")</f>
+        <v>n̄</v>
+      </c>
+      <c r="L16" s="30" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$O7,4))), "n"), "")</f>
+        <v>lǔn</v>
+      </c>
+      <c r="M16" s="30" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$O7,4))), "o"), "")</f>
+        <v>ngǒo</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="29">
+        <v>2</v>
+      </c>
+      <c r="C17" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E18,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="D17" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E18,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="E17" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E18,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="F17" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E18,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="G17" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E18,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="H17" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E18,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="I17" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E18,4))))), "")</f>
+        <v>ń</v>
+      </c>
+      <c r="L17" s="30" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$O6,4))), "n"), "")</f>
+        <v>lùn</v>
+      </c>
+      <c r="M17" s="30" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$O6,4))), "o"), "")</f>
+        <v>ngòo</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="29">
+        <v>3</v>
+      </c>
+      <c r="C18" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E19,4))))), "")</f>
+        <v>ǎ</v>
+      </c>
+      <c r="D18" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E19,4))))), "")</f>
+        <v>ǐ</v>
+      </c>
+      <c r="E18" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E19,4))))), "")</f>
+        <v>ǔ</v>
+      </c>
+      <c r="F18" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E19,4))))), "")</f>
+        <v>ě</v>
+      </c>
+      <c r="G18" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E19,4))))), "")</f>
+        <v>ǒ</v>
+      </c>
+      <c r="H18" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E19,4))))), "")</f>
+        <v>m̌</v>
+      </c>
+      <c r="I18" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E19,4))))), "")</f>
+        <v>ň</v>
+      </c>
+      <c r="L18" s="30" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$O9,4))), "n"), "")</f>
+        <v>lūn</v>
+      </c>
+      <c r="M18" s="30" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$O9,4))), "o"), "")</f>
+        <v>ngōo</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="29">
+        <v>4</v>
+      </c>
+      <c r="C19" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E20,4))))), "")</f>
+        <v>ǎ</v>
+      </c>
+      <c r="D19" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E20,4))))), "")</f>
+        <v>ǐ</v>
+      </c>
+      <c r="E19" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E20,4))))), "")</f>
+        <v>ǔ</v>
+      </c>
+      <c r="F19" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E20,4))))), "")</f>
+        <v>ě</v>
+      </c>
+      <c r="G19" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E20,4))))), "")</f>
+        <v>ǒ</v>
+      </c>
+      <c r="H19" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E20,4))))), "")</f>
+        <v>m̌</v>
+      </c>
+      <c r="I19" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E20,4))))), "")</f>
+        <v>ň</v>
+      </c>
+      <c r="L19" s="30" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$O8,4))), "n"), "")</f>
+        <v>lún</v>
+      </c>
+      <c r="M19" s="30" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$O8,4))), "o"), "")</f>
+        <v>ngóo</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="29">
+        <v>5</v>
+      </c>
+      <c r="C20" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E21,4))))), "")</f>
+        <v>à</v>
+      </c>
+      <c r="D20" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E21,4))))), "")</f>
+        <v>ì</v>
+      </c>
+      <c r="E20" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E21,4))))), "")</f>
+        <v>ù</v>
+      </c>
+      <c r="F20" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E21,4))))), "")</f>
+        <v>è</v>
+      </c>
+      <c r="G20" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E21,4))))), "")</f>
+        <v>ò</v>
+      </c>
+      <c r="H20" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E21,4))))), "")</f>
+        <v>m̀</v>
+      </c>
+      <c r="I20" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E21,4))))), "")</f>
+        <v>ǹ</v>
+      </c>
+      <c r="L20" s="30" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$O11,4))), "n"), "")</f>
+        <v>lǔn</v>
+      </c>
+      <c r="M20" s="30" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$O11,4))), "o"), "")</f>
+        <v>ngǒo</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="29">
+        <v>6</v>
+      </c>
+      <c r="C21" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E22,4))))), "")</f>
+        <v>â</v>
+      </c>
+      <c r="D21" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E22,4))))), "")</f>
+        <v>î</v>
+      </c>
+      <c r="E21" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E22,4))))), "")</f>
+        <v>û</v>
+      </c>
+      <c r="F21" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E22,4))))), "")</f>
+        <v>ê</v>
+      </c>
+      <c r="G21" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E22,4))))), "")</f>
+        <v>ô</v>
+      </c>
+      <c r="H21" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E22,4))))), "")</f>
+        <v>m̂</v>
+      </c>
+      <c r="I21" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E22,4))))), "")</f>
+        <v>n̂</v>
+      </c>
+      <c r="L21" s="30" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$O5,4))), "n"), "")</f>
+        <v>lûn</v>
+      </c>
+      <c r="M21" s="30" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$O5,4))), "o"), "")</f>
+        <v>ngôo</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B22" s="29">
+        <v>7</v>
+      </c>
+      <c r="C22" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E23,4))))), "")</f>
+        <v>ā</v>
+      </c>
+      <c r="D22" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E23,4))))), "")</f>
+        <v>ī</v>
+      </c>
+      <c r="E22" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E23,4))))), "")</f>
+        <v>ū</v>
+      </c>
+      <c r="F22" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E23,4))))), "")</f>
+        <v>ē</v>
+      </c>
+      <c r="G22" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E23,4))))), "")</f>
+        <v>ō</v>
+      </c>
+      <c r="H22" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E23,4))))), "")</f>
+        <v>m̄</v>
+      </c>
+      <c r="I22" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E23,4))))), "")</f>
+        <v>n̄</v>
+      </c>
+      <c r="L22" s="30" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$O10,4))), "n"), "")</f>
+        <v>lún</v>
+      </c>
+      <c r="M22" s="30" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$O10,4))), "o"), "")</f>
+        <v>ngóo</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B23" s="29">
+        <v>8</v>
+      </c>
+      <c r="C23" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E24,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="D23" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E24,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="E23" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E24,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="F23" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E24,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="G23" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E24,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="H23" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E24,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="I23" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E24,4))))), "")</f>
+        <v>ń</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="29"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="29"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C28" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="D28" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="E28" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="F28" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="G28" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="H28" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="I28" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="L28" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="M28" s="30" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B29" s="29">
+        <v>1</v>
+      </c>
+      <c r="C29" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E28,4))))), "")</f>
+        <v>a</v>
+      </c>
+      <c r="D29" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E28,4))))), "")</f>
+        <v>i</v>
+      </c>
+      <c r="E29" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E28,4))))), "")</f>
+        <v>u</v>
+      </c>
+      <c r="F29" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E28,4))))), "")</f>
+        <v>e</v>
+      </c>
+      <c r="G29" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E28,4))))), "")</f>
+        <v>o</v>
+      </c>
+      <c r="H29" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E28,4))))), "")</f>
+        <v>m</v>
+      </c>
+      <c r="I29" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$E28,4))))), "")</f>
+        <v>n</v>
+      </c>
+      <c r="L29" s="31" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]調表!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M4,4))))), "")</f>
+        <v>lo</v>
+      </c>
+      <c r="M29" s="31" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]調表!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M4,4)))), "r", IF(OR(B29=4, B29=8), "k", "")), "")</f>
+        <v>lor</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B30" s="29">
+        <v>2</v>
+      </c>
+      <c r="C30" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="D30" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="E30" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="F30" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="G30" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="H30" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="I30" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="L30" s="31" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]調表!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M6,4))))), "")</f>
+        <v>ló</v>
+      </c>
+      <c r="M30" s="31" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]調表!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M6,4)))), "r", IF(OR(B30=4, B30=8), "k", "")), "")</f>
+        <v>lór</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B31" s="29">
+        <v>3</v>
+      </c>
+      <c r="C31" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M4,4))))), "")</f>
+        <v>a</v>
+      </c>
+      <c r="D31" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M4,4))))), "")</f>
+        <v>i</v>
+      </c>
+      <c r="E31" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M4,4))))), "")</f>
+        <v>u</v>
+      </c>
+      <c r="F31" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M4,4))))), "")</f>
+        <v>e</v>
+      </c>
+      <c r="G31" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M4,4))))), "")</f>
+        <v>o</v>
+      </c>
+      <c r="H31" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M4,4))))), "")</f>
+        <v>m</v>
+      </c>
+      <c r="I31" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M4,4))))), "")</f>
+        <v>n</v>
+      </c>
+      <c r="L31" s="31" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]調表!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M7,4))))), "")</f>
+        <v>lò</v>
+      </c>
+      <c r="M31" s="31" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]調表!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M7,4)))), "r", IF(OR(B31=4, B31=8), "k", "")), "")</f>
+        <v>lòr</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B32" s="29">
+        <v>4</v>
+      </c>
+      <c r="C32" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M6,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="D32" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M6,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="E32" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M6,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="F32" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M6,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="G32" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M6,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="H32" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M6,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="I32" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M6,4))))), "")</f>
+        <v>ń</v>
+      </c>
+      <c r="L32" s="31" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]調表!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M8,4)))), "k"), "")</f>
+        <v>lók</v>
+      </c>
+      <c r="M32" s="31" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]調表!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M8,4)))), "r", IF(OR(B32=4, B32=8), "k", "")), "")</f>
+        <v>lórk</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B33" s="29">
+        <v>5</v>
+      </c>
+      <c r="C33" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M7,4))))), "")</f>
+        <v>à</v>
+      </c>
+      <c r="D33" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M7,4))))), "")</f>
+        <v>ì</v>
+      </c>
+      <c r="E33" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M7,4))))), "")</f>
+        <v>ù</v>
+      </c>
+      <c r="F33" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M7,4))))), "")</f>
+        <v>è</v>
+      </c>
+      <c r="G33" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M7,4))))), "")</f>
+        <v>ò</v>
+      </c>
+      <c r="H33" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M7,4))))), "")</f>
+        <v>m̀</v>
+      </c>
+      <c r="I33" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M7,4))))), "")</f>
+        <v>ǹ</v>
+      </c>
+      <c r="L33" s="31" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]調表!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M9,4))))), "")</f>
+        <v>lǒ</v>
+      </c>
+      <c r="M33" s="31" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]調表!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M9,4)))), "r", IF(OR(B33=4, B33=8), "k", "")), "")</f>
+        <v>lǒr</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B34" s="29">
+        <v>6</v>
+      </c>
+      <c r="C34" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M8,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="D34" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M8,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="E34" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M8,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="F34" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M8,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="G34" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M8,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="H34" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M8,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="I34" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M8,4))))), "")</f>
+        <v>ń</v>
+      </c>
+      <c r="L34" s="31" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]調表!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M11,4))))), "")</f>
+        <v>ló</v>
+      </c>
+      <c r="M34" s="31" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]調表!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M11,4)))), "r", IF(OR(B34=4, B34=8), "k", "")), "")</f>
+        <v>lór</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B35" s="29">
+        <v>7</v>
+      </c>
+      <c r="C35" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M9,4))))), "")</f>
+        <v>ǎ</v>
+      </c>
+      <c r="D35" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M9,4))))), "")</f>
+        <v>ǐ</v>
+      </c>
+      <c r="E35" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M9,4))))), "")</f>
+        <v>ǔ</v>
+      </c>
+      <c r="F35" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M9,4))))), "")</f>
+        <v>ě</v>
+      </c>
+      <c r="G35" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M9,4))))), "")</f>
+        <v>ǒ</v>
+      </c>
+      <c r="H35" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M9,4))))), "")</f>
+        <v>m̌</v>
+      </c>
+      <c r="I35" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M9,4))))), "")</f>
+        <v>ň</v>
+      </c>
+      <c r="L35" s="31" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]調表!$M5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M5,4))))), "")</f>
+        <v>lō</v>
+      </c>
+      <c r="M35" s="31" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]調表!$M5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M5,4)))), "r", IF(OR(B35=4, B35=8), "k", "")), "")</f>
+        <v>lōr</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B36" s="29">
+        <v>8</v>
+      </c>
+      <c r="C36" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(D$2, IF([1]調表!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M11,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="D36" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(E$2, IF([1]調表!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M11,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="E36" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(F$2, IF([1]調表!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M11,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="F36" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(G$2, IF([1]調表!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M11,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="G36" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(H$2, IF([1]調表!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M11,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="H36" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(I$2, IF([1]調表!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M11,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="I36" s="35" t="str">
+        <f>IFERROR( _xlfn.CONCAT(J$2, IF([1]調表!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M11,4))))), "")</f>
+        <v>ń</v>
+      </c>
+      <c r="L36" s="31" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]調表!$M10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M10,4)))), "k"), "")</f>
+        <v>lo̍k</v>
+      </c>
+      <c r="M36" s="31" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]調表!$M10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]調表!$M10,4)))), "r", IF(OR(B36=4, B36=8), "k", "")), "")</f>
+        <v>lo̍rk</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1F8C470-8CC3-4CDE-9E5D-92655DD9F0E1}">
+  <dimension ref="B2:C12"/>
+  <sheetFormatPr defaultRowHeight="25.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="38">
+        <v>1</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="38">
+        <v>2</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="38">
+        <v>3</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="38">
+        <v>4</v>
+      </c>
+      <c r="C6" s="39" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="38">
+        <v>5</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="B8" s="40">
+        <v>6</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="38">
+        <v>7</v>
+      </c>
+      <c r="C9" s="39" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="38">
+        <v>8</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="38">
+        <v>9</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="41">
+        <v>0</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>241</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A5E14C6-E6F0-4339-91C7-086E0286AB9D}">
+  <dimension ref="B2:R17"/>
   <sheetFormatPr defaultRowHeight="34.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="7"/>
-    <col min="2" max="2" width="9" style="8"/>
-    <col min="3" max="3" width="25.625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="25.625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="32.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="20.125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="27.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.125" style="7" customWidth="1"/>
+    <col min="10" max="10" width="20.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="9" style="7"/>
+    <col min="14" max="14" width="23" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="8" style="7" customWidth="1"/>
+    <col min="17" max="17" width="11.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="32.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:18" ht="45.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2" s="11"/>
+      <c r="G2" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="L2" s="7">
+        <f xml:space="preserve"> FIND("(",$K2)</f>
+        <v>3</v>
+      </c>
+      <c r="M2" s="7">
+        <f xml:space="preserve"> FIND(")",$K2)</f>
+        <v>10</v>
+      </c>
+      <c r="N2" s="7" t="str">
+        <f>MID(K2,L2+1,M2-L2-1)</f>
+        <v>U+0301</v>
+      </c>
+      <c r="O2" s="7">
+        <f xml:space="preserve"> FIND("（",$J2)</f>
+        <v>3</v>
+      </c>
+      <c r="P2" s="7">
+        <f xml:space="preserve"> FIND("）",$J2)</f>
+        <v>6</v>
+      </c>
+      <c r="Q2" s="7" t="str">
+        <f>MID(J2,O2+1,2)</f>
+        <v>二聲</v>
+      </c>
+      <c r="R2" s="7" t="str">
+        <f>Q2 &amp; "（" &amp; LEFT(J2,2) &amp; "）"</f>
+        <v>二聲（陰上）</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B3" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" s="16" t="str">
+        <f>_xlfn.CONCAT(C3,_xlfn.UNICHAR(HEX2DEC(RIGHT(B3,4))))</f>
+        <v>ã</v>
+      </c>
+      <c r="G3" s="7">
+        <v>771</v>
+      </c>
+      <c r="H3" s="7" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(G3,4)</f>
+        <v>U+0303</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="L3" s="7">
+        <f t="shared" ref="L3:L8" si="0" xml:space="preserve"> FIND("(",$K3)</f>
+        <v>3</v>
+      </c>
+      <c r="M3" s="7">
+        <f t="shared" ref="M3:M8" si="1" xml:space="preserve"> FIND(")",$K3)</f>
+        <v>10</v>
+      </c>
+      <c r="N3" s="7" t="str">
+        <f t="shared" ref="N3:N8" si="2">MID(K3,L3+1,M3-L3-1)</f>
+        <v>U+0300</v>
+      </c>
+      <c r="O3" s="7">
+        <f t="shared" ref="O3:O8" si="3" xml:space="preserve"> FIND("（",$J3)</f>
+        <v>3</v>
+      </c>
+      <c r="P3" s="7">
+        <f t="shared" ref="P3:P8" si="4" xml:space="preserve"> FIND("）",$J3)</f>
+        <v>6</v>
+      </c>
+      <c r="Q3" s="7" t="str">
+        <f t="shared" ref="Q3:Q8" si="5">MID(J3,O3+1,2)</f>
+        <v>三聲</v>
+      </c>
+      <c r="R3" s="7" t="str">
+        <f t="shared" ref="R3:R7" si="6">Q3 &amp; "（" &amp; LEFT(J3,2) &amp; "）"</f>
+        <v>三聲（陰去）</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="16" t="str">
+        <f t="shared" ref="D4:D5" si="7">_xlfn.CONCAT(C4,_xlfn.UNICHAR(HEX2DEC(RIGHT(B4,4))))</f>
+        <v>aʔ</v>
+      </c>
+      <c r="G4" s="7">
+        <v>660</v>
+      </c>
+      <c r="H4" s="7" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(G4,4)</f>
+        <v>U+0294</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="M4" s="7">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N4" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>U+0302</v>
+      </c>
+      <c r="O4" s="7">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="P4" s="7">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="Q4" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>五聲</v>
+      </c>
+      <c r="R4" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>五聲（陽平）</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B5" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>o͘</v>
+      </c>
+      <c r="G5" s="7">
+        <v>856</v>
+      </c>
+      <c r="H5" s="7" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(G5,4)</f>
+        <v>U+0358</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="M5" s="7">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N5" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>U+030C</v>
+      </c>
+      <c r="O5" s="7">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="P5" s="7">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="Q5" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>六聲</v>
+      </c>
+      <c r="R5" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>六聲（陽上）</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="J6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="M6" s="7">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N6" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>U+0304</v>
+      </c>
+      <c r="O6" s="7">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="P6" s="7">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="Q6" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>七聲</v>
+      </c>
+      <c r="R6" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>七聲（陽去）</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" ht="45.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L7" s="7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="M7" s="7">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="N7" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>U+030D</v>
+      </c>
+      <c r="O7" s="7">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="P7" s="7">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="Q7" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>八聲</v>
+      </c>
+      <c r="R7" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>八聲（陽入）</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="M8" s="7">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N8" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>U+030B</v>
+      </c>
+      <c r="O8" s="7">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P8" s="7">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="Q8" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>九聲</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" ht="45.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" s="16" t="str">
+        <f>_xlfn.CONCAT(C10,_xlfn.UNICHAR(HEX2DEC(RIGHT(B10,4))))</f>
+        <v>á</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="16" t="str">
+        <f t="shared" ref="D11:D17" si="8">_xlfn.CONCAT(C11,_xlfn.UNICHAR(HEX2DEC(RIGHT(B11,4))))</f>
+        <v>à</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" s="16" t="str">
+        <f t="shared" si="8"/>
+        <v>â</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" s="16" t="str">
+        <f t="shared" si="8"/>
+        <v>ǎ</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D14" s="16" t="str">
+        <f t="shared" si="8"/>
+        <v>ā</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" s="16" t="str">
+        <f t="shared" si="8"/>
+        <v>a̍</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B16" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D16" s="16" t="str">
+        <f t="shared" si="8"/>
+        <v>a̋</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" s="16" t="str">
+        <f t="shared" si="8"/>
+        <v>a̋</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDE21D6C-42DF-494D-A346-039E570FFD2A}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="34.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="32.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="36" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="14">
+        <f xml:space="preserve"> _xlfn.UNICODE(A2)</f>
+        <v>225</v>
+      </c>
+      <c r="C2" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B2,4)</f>
+        <v>U+00E1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="14">
+        <f xml:space="preserve"> _xlfn.UNICODE(A3)</f>
+        <v>244</v>
+      </c>
+      <c r="C3" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B3,4)</f>
+        <v>U+00F4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="14">
+        <f xml:space="preserve"> _xlfn.UNICODE(A4)</f>
+        <v>111</v>
+      </c>
+      <c r="C4" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B4,4)</f>
+        <v>U+006F</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="14">
+        <f xml:space="preserve"> _xlfn.UNICODE(A5)</f>
+        <v>12581</v>
+      </c>
+      <c r="C5" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B5,4)</f>
+        <v>U+3125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="14">
+        <f xml:space="preserve"> _xlfn.UNICODE(A6)</f>
+        <v>12717</v>
+      </c>
+      <c r="C6" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B6,4)</f>
+        <v>U+31AD</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="14">
+        <f xml:space="preserve"> _xlfn.UNICODE(A7)</f>
+        <v>601</v>
+      </c>
+      <c r="C7" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B7,4)</f>
+        <v>U+0259</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" s="14">
+        <f xml:space="preserve"> _xlfn.UNICODE(A8)</f>
+        <v>331</v>
+      </c>
+      <c r="C8" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B8,4)</f>
+        <v>U+014B</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="14"/>
+      <c r="C9" s="8"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C10" s="8"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" s="8"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C12" s="8"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C13" s="8"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C14" s="8"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{994B770E-8D5A-4C46-9659-8754465EA2E7}">
+  <dimension ref="B2:J11"/>
+  <sheetFormatPr defaultRowHeight="34.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9" style="7"/>
+    <col min="2" max="2" width="32.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="22.625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="21.75" style="7" customWidth="1"/>
+    <col min="6" max="9" width="9" style="7"/>
+    <col min="10" max="10" width="13.375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="20" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" style="7"/>
+    <col min="14" max="14" width="32.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="20.125" style="7" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" ht="35.25" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:10" ht="46.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" s="7" t="str">
+        <f>_xlfn.CONCAT(C4,_xlfn.UNICHAR(HEX2DEC(RIGHT(B4,4))))</f>
+        <v>ĩ</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" s="7" t="str">
+        <f>_xlfn.CONCAT(C5,_xlfn.UNICHAR(HEX2DEC(RIGHT(B5,4))))</f>
+        <v>ã</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="7" t="str">
+        <f>_xlfn.CONCAT(C6,_xlfn.UNICHAR(HEX2DEC(RIGHT(B6,4))))</f>
+        <v>ũ</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="B8" s="7"/>
+      <c r="C8" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C9" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D9" s="7" t="str">
+        <f>D4</f>
+        <v>ĩ</v>
+      </c>
+      <c r="E9" s="7" t="str">
+        <f>D9</f>
+        <v>ĩ</v>
+      </c>
+      <c r="G9" s="7" t="str">
+        <f>D9 &amp; ", " &amp; D10 &amp; ", " &amp; D11</f>
+        <v>ĩ, ĩã, ĩãũ</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C10" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" s="7" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(D4,D5)</f>
+        <v>ĩã</v>
+      </c>
+      <c r="E10" s="7" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("i",D5)</f>
+        <v>iã</v>
+      </c>
+      <c r="G10" s="7" t="str">
+        <f>D10 &amp; ", " &amp; E10 &amp; ", " &amp; E11</f>
+        <v>ĩã, iã, iãu</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="36" x14ac:dyDescent="0.25">
+      <c r="C11" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="D11" s="7" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(D9,D5,D6)</f>
+        <v>ĩãũ</v>
+      </c>
+      <c r="E11" s="7" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("i",D5,"u")</f>
+        <v>iãu</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBE671D5-EBE5-45CC-B709-0B4283CF68A0}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="34.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="32.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.125" style="7" customWidth="1"/>
     <col min="5" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>149</v>
+      </c>
       <c r="C1" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="C2" s="8">
-        <f xml:space="preserve"> _xlfn.UNICODE(B2)</f>
-        <v>225</v>
-      </c>
-      <c r="D2" s="8" t="str">
-        <f xml:space="preserve"> "U+00" &amp; TEXT( DEC2HEX(C2), "00")</f>
-        <v>U+00E1</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C3" s="8">
-        <f xml:space="preserve"> _xlfn.UNICODE(B3)</f>
-        <v>244</v>
-      </c>
-      <c r="D3" s="8" t="str">
-        <f xml:space="preserve"> "U+00" &amp; TEXT( DEC2HEX(C3), "00")</f>
-        <v>U+00F4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" s="8">
-        <f xml:space="preserve"> LEN(B5)</f>
-        <v>2</v>
-      </c>
-      <c r="D5" s="7" t="str">
-        <f xml:space="preserve"> LEFT(B5)</f>
-        <v>ō</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" s="28">
+        <f xml:space="preserve"> _xlfn.UNICODE(A2)</f>
+        <v>660</v>
+      </c>
+      <c r="C2" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B2,4)</f>
+        <v>U+0294</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="H2" s="7" t="str">
+        <f xml:space="preserve"> RIGHT(G2)</f>
+        <v>̚</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="B3" s="28">
+        <f xml:space="preserve"> _xlfn.UNICODE(A3)</f>
+        <v>794</v>
+      </c>
+      <c r="C3" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B3,4)</f>
+        <v>U+031A</v>
+      </c>
+      <c r="D3" s="27" t="str">
+        <f xml:space="preserve"> "入聲韻尾 " &amp; RIGHT(G2,2)</f>
+        <v>入聲韻尾 p̚</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H3" s="7" t="str">
+        <f xml:space="preserve"> RIGHT(G3)</f>
+        <v>ʔ</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B4" s="28">
+        <f xml:space="preserve"> _xlfn.UNICODE(A4)</f>
+        <v>771</v>
+      </c>
+      <c r="C4" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B4,4)</f>
+        <v>U+0303</v>
+      </c>
+      <c r="D4" s="27" t="str">
+        <f xml:space="preserve"> "鼻音韻母 " &amp; G4</f>
+        <v>鼻音韻母 ã</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="H4" s="7" t="str">
+        <f xml:space="preserve"> RIGHT(G4)</f>
+        <v>̃</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B5" s="28">
+        <f xml:space="preserve"> _xlfn.UNICODE(A5)</f>
+        <v>650</v>
+      </c>
+      <c r="C5" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B5,4)</f>
+        <v>U+028A</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="H5" s="7" t="str">
+        <f xml:space="preserve"> RIGHT(G5)</f>
+        <v>ʊ</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="B6" s="28">
+        <f xml:space="preserve"> _xlfn.UNICODE(A6)</f>
+        <v>618</v>
+      </c>
+      <c r="C6" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B6,4)</f>
+        <v>U+026A</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="H6" s="7" t="str">
+        <f xml:space="preserve"> RIGHT(G6)</f>
+        <v>ɪ</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="28">
+        <f xml:space="preserve"> _xlfn.UNICODE(A7)</f>
+        <v>331</v>
+      </c>
+      <c r="C7" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B7,4)</f>
+        <v>U+014B</v>
+      </c>
+      <c r="D7" s="8"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="B8" s="28">
+        <f xml:space="preserve"> _xlfn.UNICODE(A8)</f>
+        <v>601</v>
+      </c>
+      <c r="C8" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B8,4)</f>
+        <v>U+0259</v>
+      </c>
+      <c r="D8" s="8"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="B9" s="28">
+        <f xml:space="preserve"> _xlfn.UNICODE(A9)</f>
+        <v>603</v>
+      </c>
+      <c r="C9" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B9,4)</f>
+        <v>U+025B</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="G9" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B10" s="28">
+        <f xml:space="preserve"> _xlfn.UNICODE(A10)</f>
+        <v>596</v>
+      </c>
+      <c r="C10" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B10,4)</f>
+        <v>U+0254</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="G10" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B11" s="28">
+        <f xml:space="preserve"> _xlfn.UNICODE(A11)</f>
+        <v>109</v>
+      </c>
+      <c r="C11" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B11,4)</f>
+        <v>U+006D</v>
+      </c>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="B12" s="28">
+        <f xml:space="preserve"> _xlfn.UNICODE(A12)</f>
+        <v>331</v>
+      </c>
+      <c r="C12" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B12,4)</f>
+        <v>U+014B</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="28">
+        <f xml:space="preserve"> _xlfn.UNICODE(A13)</f>
+        <v>8319</v>
+      </c>
+      <c r="C13" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B13,4)</f>
+        <v>U+207F</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="28"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="28"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B16" s="28">
+        <f xml:space="preserve"> _xlfn.UNICODE(A16)</f>
+        <v>12581</v>
+      </c>
+      <c r="C16" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B16,4)</f>
+        <v>U+3125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="B17" s="28">
+        <f xml:space="preserve"> _xlfn.UNICODE(A17)</f>
+        <v>12717</v>
+      </c>
+      <c r="C17" s="8" t="str">
+        <f xml:space="preserve"> "U+" &amp; DEC2HEX(B17,4)</f>
+        <v>U+31AD</v>
       </c>
     </row>
   </sheetData>
